--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/61.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/61.xlsx
@@ -426,13 +426,13 @@
         <v>-8.997635557753098</v>
       </c>
       <c r="E2">
-        <v>-24.925760035473</v>
+        <v>-26.69999350930821</v>
       </c>
       <c r="F2">
-        <v>-4.948469031762485</v>
+        <v>-4.187413935747065</v>
       </c>
       <c r="G2">
-        <v>-12.89583403343453</v>
+        <v>-13.32405309893926</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.115236432712203</v>
       </c>
       <c r="E3">
-        <v>-23.31493654620458</v>
+        <v>-27.55671739292334</v>
       </c>
       <c r="F3">
-        <v>-4.285093363150377</v>
+        <v>-3.867305435181043</v>
       </c>
       <c r="G3">
-        <v>-12.68601165715552</v>
+        <v>-13.15667853756479</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.144189616003034</v>
       </c>
       <c r="E4">
-        <v>-26.59693902631566</v>
+        <v>-27.22298244398005</v>
       </c>
       <c r="F4">
-        <v>-4.48149927435414</v>
+        <v>-3.526569757917911</v>
       </c>
       <c r="G4">
-        <v>-14.17645733020911</v>
+        <v>-13.15864169106957</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.074657853342812</v>
       </c>
       <c r="E5">
-        <v>-25.75450247819473</v>
+        <v>-27.5882219865947</v>
       </c>
       <c r="F5">
-        <v>-4.202269048381468</v>
+        <v>-4.023567833677739</v>
       </c>
       <c r="G5">
-        <v>-14.04351740826137</v>
+        <v>-13.202218402003</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.90545416382122</v>
       </c>
       <c r="E6">
-        <v>-24.79700646248692</v>
+        <v>-25.66398281125541</v>
       </c>
       <c r="F6">
-        <v>-4.975485406237389</v>
+        <v>-4.111660565128453</v>
       </c>
       <c r="G6">
-        <v>-11.49733379691589</v>
+        <v>-14.42704245371317</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.637298379763783</v>
       </c>
       <c r="E7">
-        <v>-25.68578288512834</v>
+        <v>-27.52514940061587</v>
       </c>
       <c r="F7">
-        <v>-4.39310004696439</v>
+        <v>-3.58339659011736</v>
       </c>
       <c r="G7">
-        <v>-13.62476815827173</v>
+        <v>-15.38896780778596</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.273905800426808</v>
       </c>
       <c r="E8">
-        <v>-25.35821118930949</v>
+        <v>-25.48023544992018</v>
       </c>
       <c r="F8">
-        <v>-3.824429138412141</v>
+        <v>-3.79990780655447</v>
       </c>
       <c r="G8">
-        <v>-13.49697944518309</v>
+        <v>-14.70886919547132</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.821744618698039</v>
       </c>
       <c r="E9">
-        <v>-27.50041034711197</v>
+        <v>-28.98246214949827</v>
       </c>
       <c r="F9">
-        <v>-3.950413879969112</v>
+        <v>-2.914045079061456</v>
       </c>
       <c r="G9">
-        <v>-13.70065744894121</v>
+        <v>-12.4670919017346</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.290963919920212</v>
       </c>
       <c r="E10">
-        <v>-26.00149450752109</v>
+        <v>-27.16440210421683</v>
       </c>
       <c r="F10">
-        <v>-3.866257550416502</v>
+        <v>-3.725575086031659</v>
       </c>
       <c r="G10">
-        <v>-14.34489126615615</v>
+        <v>-13.62942113002717</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.694749988184592</v>
       </c>
       <c r="E11">
-        <v>-26.53932777999008</v>
+        <v>-27.83947983843628</v>
       </c>
       <c r="F11">
-        <v>-3.70188874851601</v>
+        <v>-3.571147521332164</v>
       </c>
       <c r="G11">
-        <v>-13.18297751132876</v>
+        <v>-13.19878205573324</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.049232619967393</v>
       </c>
       <c r="E12">
-        <v>-27.25665164822708</v>
+        <v>-29.06067342408475</v>
       </c>
       <c r="F12">
-        <v>-3.647450927906235</v>
+        <v>-2.76473019797204</v>
       </c>
       <c r="G12">
-        <v>-13.28395246082207</v>
+        <v>-14.12229514991387</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.370699319534221</v>
       </c>
       <c r="E13">
-        <v>-27.79127423262463</v>
+        <v>-29.73838220170266</v>
       </c>
       <c r="F13">
-        <v>-2.90727317554357</v>
+        <v>-2.161474950352911</v>
       </c>
       <c r="G13">
-        <v>-13.58953567737003</v>
+        <v>-13.3983417408405</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.681596306057151</v>
       </c>
       <c r="E14">
-        <v>-25.2961076967683</v>
+        <v>-28.73686941864029</v>
       </c>
       <c r="F14">
-        <v>-2.610028443662218</v>
+        <v>-2.398291108567442</v>
       </c>
       <c r="G14">
-        <v>-11.31340650784506</v>
+        <v>-13.25427010951696</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.003173148123158</v>
       </c>
       <c r="E15">
-        <v>-27.33938233987321</v>
+        <v>-29.53114790992664</v>
       </c>
       <c r="F15">
-        <v>-3.36258863196193</v>
+        <v>-2.983013292283737</v>
       </c>
       <c r="G15">
-        <v>-12.92417892434177</v>
+        <v>-13.28603148342073</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.357147776573963</v>
       </c>
       <c r="E16">
-        <v>-28.19055884282894</v>
+        <v>-30.57974097300976</v>
       </c>
       <c r="F16">
-        <v>-2.553392964332816</v>
+        <v>-1.654721191690313</v>
       </c>
       <c r="G16">
-        <v>-13.99694630888767</v>
+        <v>-12.67514644669563</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.764806920400301</v>
       </c>
       <c r="E17">
-        <v>-30.26425124584338</v>
+        <v>-32.17891043441944</v>
       </c>
       <c r="F17">
-        <v>-2.964288047143455</v>
+        <v>-2.135933898222394</v>
       </c>
       <c r="G17">
-        <v>-12.06424485724284</v>
+        <v>-13.40851173673714</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.245136911440341</v>
       </c>
       <c r="E18">
-        <v>-28.25846331057396</v>
+        <v>-32.40254459481423</v>
       </c>
       <c r="F18">
-        <v>-3.408143040544083</v>
+        <v>-1.993366897996182</v>
       </c>
       <c r="G18">
-        <v>-12.20811785583403</v>
+        <v>-12.54766064852384</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.814865639052698</v>
       </c>
       <c r="E19">
-        <v>-30.2176260774604</v>
+        <v>-29.74150458453094</v>
       </c>
       <c r="F19">
-        <v>-2.211984652738611</v>
+        <v>-1.611390949584677</v>
       </c>
       <c r="G19">
-        <v>-11.92718827191702</v>
+        <v>-12.17447278151842</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.48689091838336</v>
       </c>
       <c r="E20">
-        <v>-30.78309436256119</v>
+        <v>-29.3606214284568</v>
       </c>
       <c r="F20">
-        <v>-2.648743022599456</v>
+        <v>-2.090041515739898</v>
       </c>
       <c r="G20">
-        <v>-11.86831021950108</v>
+        <v>-13.503209891888</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.27006148534303</v>
       </c>
       <c r="E21">
-        <v>-29.94392963691081</v>
+        <v>-32.98763475779026</v>
       </c>
       <c r="F21">
-        <v>-2.215057895802997</v>
+        <v>-1.588962073786477</v>
       </c>
       <c r="G21">
-        <v>-12.22070454997434</v>
+        <v>-12.22657745776101</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.16882890395818</v>
       </c>
       <c r="E22">
-        <v>-29.11631478421699</v>
+        <v>-31.24143706653654</v>
       </c>
       <c r="F22">
-        <v>-1.862713477757033</v>
+        <v>-0.9603032830256962</v>
       </c>
       <c r="G22">
-        <v>-11.29460591972754</v>
+        <v>-12.58883059285022</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.183684511592438</v>
       </c>
       <c r="E23">
-        <v>-29.96603538277926</v>
+        <v>-33.69038146819658</v>
       </c>
       <c r="F23">
-        <v>-2.048208961898523</v>
+        <v>-1.698880629566152</v>
       </c>
       <c r="G23">
-        <v>-11.26156005415453</v>
+        <v>-11.73030681815102</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.31057656406998</v>
       </c>
       <c r="E24">
-        <v>-30.71427967154064</v>
+        <v>-33.02004051778915</v>
       </c>
       <c r="F24">
-        <v>-1.159186841131232</v>
+        <v>-1.244562527500763</v>
       </c>
       <c r="G24">
-        <v>-12.00111937490002</v>
+        <v>-11.25327706921528</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.540687433479669</v>
       </c>
       <c r="E25">
-        <v>-29.32455213298571</v>
+        <v>-32.24083278800032</v>
       </c>
       <c r="F25">
-        <v>-1.77668917971111</v>
+        <v>-1.756973207157079</v>
       </c>
       <c r="G25">
-        <v>-11.53723911284626</v>
+        <v>-12.83532388206773</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.861605518603165</v>
       </c>
       <c r="E26">
-        <v>-29.7504551134071</v>
+        <v>-30.83503822366618</v>
       </c>
       <c r="F26">
-        <v>-1.754043271653377</v>
+        <v>-1.842688524161758</v>
       </c>
       <c r="G26">
-        <v>-11.4095281975778</v>
+        <v>-12.86644301013688</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.25829521924617</v>
       </c>
       <c r="E27">
-        <v>-28.93382633865589</v>
+        <v>-31.49427988428081</v>
       </c>
       <c r="F27">
-        <v>-2.450973618650685</v>
+        <v>-1.988405805620816</v>
       </c>
       <c r="G27">
-        <v>-11.49324858372043</v>
+        <v>-12.46721108137401</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.712801903365777</v>
       </c>
       <c r="E28">
-        <v>-30.17521691837857</v>
+        <v>-31.52988953964012</v>
       </c>
       <c r="F28">
-        <v>-2.409690272397366</v>
+        <v>-2.043936242834883</v>
       </c>
       <c r="G28">
-        <v>-11.14328088312745</v>
+        <v>-11.67434535635518</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.205702402129651</v>
       </c>
       <c r="E29">
-        <v>-29.13645743660311</v>
+        <v>-30.81294832745676</v>
       </c>
       <c r="F29">
-        <v>-1.987526079439043</v>
+        <v>-1.158315398623487</v>
       </c>
       <c r="G29">
-        <v>-11.79393219287027</v>
+        <v>-13.54451887912702</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.717301325174591</v>
       </c>
       <c r="E30">
-        <v>-28.33378994721755</v>
+        <v>-32.58765502682577</v>
       </c>
       <c r="F30">
-        <v>-1.946637036069456</v>
+        <v>-1.473931662764127</v>
       </c>
       <c r="G30">
-        <v>-11.65464098930544</v>
+        <v>-13.01122971929691</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.227607517943293</v>
       </c>
       <c r="E31">
-        <v>-27.57832727088794</v>
+        <v>-30.84607864329688</v>
       </c>
       <c r="F31">
-        <v>-1.999694796586168</v>
+        <v>-1.639326811876687</v>
       </c>
       <c r="G31">
-        <v>-11.66853534893376</v>
+        <v>-13.53200501698858</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.721679144817656</v>
       </c>
       <c r="E32">
-        <v>-26.94680892814827</v>
+        <v>-32.05733675697252</v>
       </c>
       <c r="F32">
-        <v>-2.098843747762046</v>
+        <v>-1.880502667732152</v>
       </c>
       <c r="G32">
-        <v>-12.40656188709456</v>
+        <v>-12.75187496065932</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.186005639633048</v>
       </c>
       <c r="E33">
-        <v>-28.43293182866747</v>
+        <v>-30.91278985814088</v>
       </c>
       <c r="F33">
-        <v>-1.611470472855346</v>
+        <v>-2.108841313946433</v>
       </c>
       <c r="G33">
-        <v>-11.56564690411875</v>
+        <v>-10.82824936961041</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.61022638473992</v>
       </c>
       <c r="E34">
-        <v>-27.67520038686002</v>
+        <v>-28.96245987980639</v>
       </c>
       <c r="F34">
-        <v>-2.109231474993152</v>
+        <v>-2.486306801849695</v>
       </c>
       <c r="G34">
-        <v>-12.42479968247041</v>
+        <v>-11.80053011013004</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.987570104337223</v>
       </c>
       <c r="E35">
-        <v>-25.17591293965672</v>
+        <v>-29.35468459903274</v>
       </c>
       <c r="F35">
-        <v>-2.004725471823369</v>
+        <v>-2.579272818731078</v>
       </c>
       <c r="G35">
-        <v>-13.00483374531503</v>
+        <v>-12.64409684008281</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.315191854529407</v>
       </c>
       <c r="E36">
-        <v>-27.15415416753747</v>
+        <v>-29.13816919977801</v>
       </c>
       <c r="F36">
-        <v>-2.20536516882284</v>
+        <v>-1.675334286141576</v>
       </c>
       <c r="G36">
-        <v>-12.61102449014549</v>
+        <v>-13.23709830980476</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.594182843767869</v>
       </c>
       <c r="E37">
-        <v>-26.22285084549003</v>
+        <v>-29.19115687414176</v>
       </c>
       <c r="F37">
-        <v>-1.828363566665146</v>
+        <v>-1.979549729717486</v>
       </c>
       <c r="G37">
-        <v>-12.44678501539671</v>
+        <v>-12.61484154915227</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.82876442812327</v>
       </c>
       <c r="E38">
-        <v>-27.08358695707595</v>
+        <v>-29.43348683947722</v>
       </c>
       <c r="F38">
-        <v>-2.02984157147625</v>
+        <v>-1.969273832085758</v>
       </c>
       <c r="G38">
-        <v>-12.02605771444735</v>
+        <v>-12.84678168017915</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.026526501155436</v>
       </c>
       <c r="E39">
-        <v>-25.0340947191585</v>
+        <v>-27.52629510453981</v>
       </c>
       <c r="F39">
-        <v>-2.358396106081215</v>
+        <v>-1.303314485544318</v>
       </c>
       <c r="G39">
-        <v>-12.65092649553033</v>
+        <v>-12.40438023758418</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.196749111740851</v>
       </c>
       <c r="E40">
-        <v>-25.9469490380987</v>
+        <v>-27.9350713962642</v>
       </c>
       <c r="F40">
-        <v>-2.222585270392236</v>
+        <v>-1.575140763670768</v>
       </c>
       <c r="G40">
-        <v>-12.40036454584505</v>
+        <v>-12.96101867510278</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.349154790645495</v>
       </c>
       <c r="E41">
-        <v>-24.6392389565337</v>
+        <v>-26.46711673346377</v>
       </c>
       <c r="F41">
-        <v>-1.829348495507074</v>
+        <v>-2.169082676580222</v>
       </c>
       <c r="G41">
-        <v>-10.95942973660403</v>
+        <v>-14.25259822233958</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.493098724743363</v>
       </c>
       <c r="E42">
-        <v>-26.38755597362301</v>
+        <v>-28.72769473030075</v>
       </c>
       <c r="F42">
-        <v>-1.386848711177426</v>
+        <v>-2.379600654858077</v>
       </c>
       <c r="G42">
-        <v>-12.06256972119997</v>
+        <v>-10.7004755539767</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.636007970785347</v>
       </c>
       <c r="E43">
-        <v>-25.33227209019356</v>
+        <v>-29.05657968358181</v>
       </c>
       <c r="F43">
-        <v>-1.924616545400837</v>
+        <v>-1.467394187221233</v>
       </c>
       <c r="G43">
-        <v>-12.26971386613771</v>
+        <v>-10.74798850355632</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.784827914060211</v>
       </c>
       <c r="E44">
-        <v>-25.20102785650326</v>
+        <v>-26.05602639152146</v>
       </c>
       <c r="F44">
-        <v>-2.214140893088098</v>
+        <v>-2.583941497413256</v>
       </c>
       <c r="G44">
-        <v>-10.83444671085992</v>
+        <v>-12.21446748217835</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.946492776712156</v>
       </c>
       <c r="E45">
-        <v>-22.9561093227848</v>
+        <v>-25.75913057863058</v>
       </c>
       <c r="F45">
-        <v>-2.512341560952281</v>
+        <v>-1.6006271435527</v>
       </c>
       <c r="G45">
-        <v>-11.46629743248522</v>
+        <v>-11.94590278585052</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.125008740904882</v>
       </c>
       <c r="E46">
-        <v>-23.90794927445703</v>
+        <v>-29.46303739661428</v>
       </c>
       <c r="F46">
-        <v>-1.863519479239957</v>
+        <v>-1.774160174030363</v>
       </c>
       <c r="G46">
-        <v>-11.93619295578383</v>
+        <v>-13.30724214869084</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.322100209940828</v>
       </c>
       <c r="E47">
-        <v>-22.33218975943</v>
+        <v>-26.79856027455916</v>
       </c>
       <c r="F47">
-        <v>-2.250671895551556</v>
+        <v>-1.178714774284828</v>
       </c>
       <c r="G47">
-        <v>-10.79130699193768</v>
+        <v>-11.60126837412131</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.537194620483344</v>
       </c>
       <c r="E48">
-        <v>-23.44582303044828</v>
+        <v>-25.66485680673889</v>
       </c>
       <c r="F48">
-        <v>-2.018558379082718</v>
+        <v>-1.646343083778399</v>
       </c>
       <c r="G48">
-        <v>-9.393892614355918</v>
+        <v>-12.29858182324016</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.767261296066046</v>
       </c>
       <c r="E49">
-        <v>-22.0266083333924</v>
+        <v>-25.28085579631047</v>
       </c>
       <c r="F49">
-        <v>-2.887295438890255</v>
+        <v>-1.882636542161764</v>
       </c>
       <c r="G49">
-        <v>-11.44951627714665</v>
+        <v>-12.26110975828114</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.007038519041606</v>
       </c>
       <c r="E50">
-        <v>-23.06333453033842</v>
+        <v>-25.9128224579769</v>
       </c>
       <c r="F50">
-        <v>-2.818922821830586</v>
+        <v>-1.905852366992623</v>
       </c>
       <c r="G50">
-        <v>-11.09319232911828</v>
+        <v>-10.65183701891372</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.248626177102174</v>
       </c>
       <c r="E51">
-        <v>-20.24440021682969</v>
+        <v>-25.75266391774762</v>
       </c>
       <c r="F51">
-        <v>-2.967516194912164</v>
+        <v>-1.914750689633495</v>
       </c>
       <c r="G51">
-        <v>-9.758168492769624</v>
+        <v>-12.40708164274423</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.485855508080903</v>
       </c>
       <c r="E52">
-        <v>-22.53756964109987</v>
+        <v>-24.57185073482555</v>
       </c>
       <c r="F52">
-        <v>-2.941159200889889</v>
+        <v>-2.186577796127347</v>
       </c>
       <c r="G52">
-        <v>-10.89473836622113</v>
+        <v>-11.95511603408631</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.710138810410928</v>
       </c>
       <c r="E53">
-        <v>-21.99981788116303</v>
+        <v>-24.96075155413028</v>
       </c>
       <c r="F53">
-        <v>-3.46826843174148</v>
+        <v>-2.351837092985849</v>
       </c>
       <c r="G53">
-        <v>-11.87331576435646</v>
+        <v>-13.13648752032077</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.912766189203273</v>
       </c>
       <c r="E54">
-        <v>-21.43421600607901</v>
+        <v>-24.68494484469311</v>
       </c>
       <c r="F54">
-        <v>-3.053853615836346</v>
+        <v>-1.032666974232053</v>
       </c>
       <c r="G54">
-        <v>-10.35942646306652</v>
+        <v>-11.88310835806162</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.08566196903444</v>
       </c>
       <c r="E55">
-        <v>-22.60241286041571</v>
+        <v>-26.77716323487292</v>
       </c>
       <c r="F55">
-        <v>-2.981413714828931</v>
+        <v>-1.743360645626874</v>
       </c>
       <c r="G55">
-        <v>-11.74684961421076</v>
+        <v>-12.46058005865885</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-10.21965906471728</v>
       </c>
       <c r="E56">
-        <v>-21.33418654372358</v>
+        <v>-25.00507625771735</v>
       </c>
       <c r="F56">
-        <v>-3.507280394576322</v>
+        <v>-1.458705441533269</v>
       </c>
       <c r="G56">
-        <v>-11.48310176164256</v>
+        <v>-12.3793194078519</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.31114131163869</v>
       </c>
       <c r="E57">
-        <v>-20.77556304708538</v>
+        <v>-23.9536868619345</v>
       </c>
       <c r="F57">
-        <v>-3.456260417870498</v>
+        <v>-2.285816210982728</v>
       </c>
       <c r="G57">
-        <v>-11.69192435316871</v>
+        <v>-11.53532230697903</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.35716000044505</v>
       </c>
       <c r="E58">
-        <v>-22.04485808364332</v>
+        <v>-23.19913440888044</v>
       </c>
       <c r="F58">
-        <v>-3.10860207422217</v>
+        <v>-1.55783451189148</v>
       </c>
       <c r="G58">
-        <v>-12.06286104920743</v>
+        <v>-11.26858503178887</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.35635980224305</v>
       </c>
       <c r="E59">
-        <v>-21.26120112814195</v>
+        <v>-24.10823915134229</v>
       </c>
       <c r="F59">
-        <v>-3.411638750983897</v>
+        <v>-2.271757159422415</v>
       </c>
       <c r="G59">
-        <v>-9.696291086095107</v>
+        <v>-11.50114092428605</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.30917598816853</v>
       </c>
       <c r="E60">
-        <v>-20.1169417874098</v>
+        <v>-24.01931803572767</v>
       </c>
       <c r="F60">
-        <v>-3.258787569451929</v>
+        <v>-1.94112259426902</v>
       </c>
       <c r="G60">
-        <v>-9.358019542892377</v>
+        <v>-12.14450903384247</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.2182717812134</v>
       </c>
       <c r="E61">
-        <v>-22.48585446793228</v>
+        <v>-23.36797403378242</v>
       </c>
       <c r="F61">
-        <v>-3.479597184342166</v>
+        <v>-2.52769535076317</v>
       </c>
       <c r="G61">
-        <v>-11.97665113281927</v>
+        <v>-12.16199864592644</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.08801267921406</v>
       </c>
       <c r="E62">
-        <v>-22.01193154913355</v>
+        <v>-23.60249464569165</v>
       </c>
       <c r="F62">
-        <v>-3.550009241947526</v>
+        <v>-2.441849151708849</v>
       </c>
       <c r="G62">
-        <v>-11.37177473624795</v>
+        <v>-11.69691334529639</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.923186823449898</v>
       </c>
       <c r="E63">
-        <v>-21.79170732966653</v>
+        <v>-25.17792811059013</v>
       </c>
       <c r="F63">
-        <v>-3.411982523456059</v>
+        <v>-2.367106389321652</v>
       </c>
       <c r="G63">
-        <v>-10.53879513092977</v>
+        <v>-11.45320753542294</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.731432351770911</v>
       </c>
       <c r="E64">
-        <v>-22.62345215065534</v>
+        <v>-23.67953304551014</v>
       </c>
       <c r="F64">
-        <v>-3.263756945501323</v>
+        <v>-2.58521801158097</v>
       </c>
       <c r="G64">
-        <v>-10.46648950580655</v>
+        <v>-11.74442298433047</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.522252303642063</v>
       </c>
       <c r="E65">
-        <v>-22.44311020177388</v>
+        <v>-22.8864432786508</v>
       </c>
       <c r="F65">
-        <v>-3.591749847007191</v>
+        <v>-2.696726204406617</v>
       </c>
       <c r="G65">
-        <v>-11.07845046983191</v>
+        <v>-11.55726791335885</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.304405152956438</v>
       </c>
       <c r="E66">
-        <v>-22.08744385321145</v>
+        <v>-24.66857893962939</v>
       </c>
       <c r="F66">
-        <v>-3.484382662828138</v>
+        <v>-2.672329956026769</v>
       </c>
       <c r="G66">
-        <v>-11.17691271526091</v>
+        <v>-11.5983087464092</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.086710019949971</v>
       </c>
       <c r="E67">
-        <v>-21.43355032039988</v>
+        <v>-26.61077351440909</v>
       </c>
       <c r="F67">
-        <v>-3.801668915652822</v>
+        <v>-2.761303242026658</v>
       </c>
       <c r="G67">
-        <v>-11.4593154919429</v>
+        <v>-12.09463566529335</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.876981236844212</v>
       </c>
       <c r="E68">
-        <v>-21.88554636805347</v>
+        <v>-23.6465068845722</v>
       </c>
       <c r="F68">
-        <v>-3.086294968432183</v>
+        <v>-2.247719594127979</v>
       </c>
       <c r="G68">
-        <v>-9.511188553357837</v>
+        <v>-11.9645908154197</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.681099112747832</v>
       </c>
       <c r="E69">
-        <v>-22.34799413371677</v>
+        <v>-23.14100691651798</v>
       </c>
       <c r="F69">
-        <v>-3.39632389444094</v>
+        <v>-2.860323796255102</v>
       </c>
       <c r="G69">
-        <v>-11.44216355550394</v>
+        <v>-10.98865192207917</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.505982863562954</v>
       </c>
       <c r="E70">
-        <v>-22.49359363001139</v>
+        <v>-24.27156762337693</v>
       </c>
       <c r="F70">
-        <v>-4.039293560452485</v>
+        <v>-2.113847966528954</v>
       </c>
       <c r="G70">
-        <v>-10.8292855703642</v>
+        <v>-10.52333488326137</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.355261522750514</v>
       </c>
       <c r="E71">
-        <v>-23.0097173980876</v>
+        <v>-24.17078190586222</v>
       </c>
       <c r="F71">
-        <v>-3.994142566795495</v>
+        <v>-3.34045548332653</v>
       </c>
       <c r="G71">
-        <v>-8.726423733273602</v>
+        <v>-11.95146119181095</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.230558717438203</v>
       </c>
       <c r="E72">
-        <v>-20.29986496647563</v>
+        <v>-22.98400019419804</v>
       </c>
       <c r="F72">
-        <v>-3.997257228230021</v>
+        <v>-2.810623408821938</v>
       </c>
       <c r="G72">
-        <v>-11.14627361629495</v>
+        <v>-13.09641336656789</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.131460371338392</v>
       </c>
       <c r="E73">
-        <v>-23.33780986841733</v>
+        <v>-24.83363276026096</v>
       </c>
       <c r="F73">
-        <v>-3.946015249060247</v>
+        <v>-3.453542544421913</v>
       </c>
       <c r="G73">
-        <v>-12.32810526835937</v>
+        <v>-11.51433675880559</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.055862302494887</v>
       </c>
       <c r="E74">
-        <v>-23.59504077747502</v>
+        <v>-24.89752500003518</v>
       </c>
       <c r="F74">
-        <v>-3.63988047821205</v>
+        <v>-2.779804827968185</v>
       </c>
       <c r="G74">
-        <v>-10.89512570004922</v>
+        <v>-11.73232625092998</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.000451716871277</v>
       </c>
       <c r="E75">
-        <v>-23.02121519359308</v>
+        <v>-25.91444365167164</v>
       </c>
       <c r="F75">
-        <v>-3.646770838268536</v>
+        <v>-2.730626311998784</v>
       </c>
       <c r="G75">
-        <v>-11.03813133570912</v>
+        <v>-11.63563514736448</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.959286848133879</v>
       </c>
       <c r="E76">
-        <v>-22.44378494440102</v>
+        <v>-26.35001492409942</v>
       </c>
       <c r="F76">
-        <v>-3.597075421039789</v>
+        <v>-2.638705694779734</v>
       </c>
       <c r="G76">
-        <v>-10.83916092770784</v>
+        <v>-9.550233127448001</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.930388376484416</v>
       </c>
       <c r="E77">
-        <v>-22.80547869186766</v>
+        <v>-25.07565252512689</v>
       </c>
       <c r="F77">
-        <v>-4.338291946125564</v>
+        <v>-3.386591405825448</v>
       </c>
       <c r="G77">
-        <v>-10.14743567945929</v>
+        <v>-11.23716795462118</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.910266138638553</v>
       </c>
       <c r="E78">
-        <v>-24.16206912187146</v>
+        <v>-24.83512262820948</v>
       </c>
       <c r="F78">
-        <v>-4.397921973616087</v>
+        <v>-4.227472954979046</v>
       </c>
       <c r="G78">
-        <v>-9.937828488640331</v>
+        <v>-10.92988311766603</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.895791009647562</v>
       </c>
       <c r="E79">
-        <v>-22.76935505470847</v>
+        <v>-25.27327965929564</v>
       </c>
       <c r="F79">
-        <v>-4.33874340636009</v>
+        <v>-3.280260509267298</v>
       </c>
       <c r="G79">
-        <v>-11.06625773061077</v>
+        <v>-11.16845427140807</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.884912335260414</v>
       </c>
       <c r="E80">
-        <v>-23.02376472445939</v>
+        <v>-26.40287127271695</v>
       </c>
       <c r="F80">
-        <v>-5.117262972328732</v>
+        <v>-3.104942347036602</v>
       </c>
       <c r="G80">
-        <v>-11.1665010495399</v>
+        <v>-11.87394145746338</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.875292893917966</v>
       </c>
       <c r="E81">
-        <v>-25.28289360961392</v>
+        <v>-24.91077531498162</v>
       </c>
       <c r="F81">
-        <v>-3.908760253486742</v>
+        <v>-3.888209286590689</v>
       </c>
       <c r="G81">
-        <v>-10.50453429514385</v>
+        <v>-10.90557378177116</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.867353760808604</v>
       </c>
       <c r="E82">
-        <v>-25.98545012411191</v>
+        <v>-27.84673898227058</v>
       </c>
       <c r="F82">
-        <v>-3.783818426489895</v>
+        <v>-3.892720575466335</v>
       </c>
       <c r="G82">
-        <v>-9.429858381094562</v>
+        <v>-11.20804177496668</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.863071446962341</v>
       </c>
       <c r="E83">
-        <v>-23.88892515515081</v>
+        <v>-27.77586383557653</v>
       </c>
       <c r="F83">
-        <v>-4.477270458762848</v>
+        <v>-3.393965532445169</v>
       </c>
       <c r="G83">
-        <v>-10.56174714315354</v>
+        <v>-12.00395320188164</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.864346382108194</v>
       </c>
       <c r="E84">
-        <v>-25.16457816921552</v>
+        <v>-27.11979210676727</v>
       </c>
       <c r="F84">
-        <v>-4.416762361825358</v>
+        <v>-4.264626061362007</v>
       </c>
       <c r="G84">
-        <v>-11.82570349841066</v>
+        <v>-10.53698757306533</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.873426913761961</v>
       </c>
       <c r="E85">
-        <v>-27.59465241968559</v>
+        <v>-26.58286905757383</v>
       </c>
       <c r="F85">
-        <v>-4.474490457759053</v>
+        <v>-3.501410583160085</v>
       </c>
       <c r="G85">
-        <v>-11.27427254902534</v>
+        <v>-12.50572927872343</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.892468031422422</v>
       </c>
       <c r="E86">
-        <v>-26.08640792363892</v>
+        <v>-30.01819887487361</v>
       </c>
       <c r="F86">
-        <v>-5.220373176424798</v>
+        <v>-4.299814280265527</v>
       </c>
       <c r="G86">
-        <v>-11.76951691951815</v>
+        <v>-10.28569068227033</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.923092421583969</v>
       </c>
       <c r="E87">
-        <v>-27.36164431809492</v>
+        <v>-30.98522959260457</v>
       </c>
       <c r="F87">
-        <v>-4.512616067472901</v>
+        <v>-4.644649547805114</v>
       </c>
       <c r="G87">
-        <v>-10.86549962801829</v>
+        <v>-11.96396181176724</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.965832741838674</v>
       </c>
       <c r="E88">
-        <v>-27.80016362710169</v>
+        <v>-31.04682589605691</v>
       </c>
       <c r="F88">
-        <v>-4.530183254984069</v>
+        <v>-3.964404177034993</v>
       </c>
       <c r="G88">
-        <v>-11.01867525957483</v>
+        <v>-10.39189960426123</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.020234330872455</v>
       </c>
       <c r="E89">
-        <v>-30.29341461845277</v>
+        <v>-29.28438456853767</v>
       </c>
       <c r="F89">
-        <v>-5.862586542997588</v>
+        <v>-4.825482980203648</v>
       </c>
       <c r="G89">
-        <v>-11.4446729490227</v>
+        <v>-11.05350881973904</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.087337400362481</v>
       </c>
       <c r="E90">
-        <v>-31.1134782407388</v>
+        <v>-31.65907105341993</v>
       </c>
       <c r="F90">
-        <v>-4.947673799055798</v>
+        <v>-4.551275974161553</v>
       </c>
       <c r="G90">
-        <v>-11.65740198428519</v>
+        <v>-11.31834253124411</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.165743568406429</v>
       </c>
       <c r="E91">
-        <v>-32.47434128596884</v>
+        <v>-32.066479745994</v>
       </c>
       <c r="F91">
-        <v>-4.800501076070021</v>
+        <v>-4.162733557348056</v>
       </c>
       <c r="G91">
-        <v>-11.07385212207786</v>
+        <v>-12.81995964021997</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.253495814649355</v>
       </c>
       <c r="E92">
-        <v>-33.49738243446367</v>
+        <v>-34.14898908790137</v>
       </c>
       <c r="F92">
-        <v>-5.66309330648359</v>
+        <v>-4.290216815536692</v>
       </c>
       <c r="G92">
-        <v>-9.976346685989752</v>
+        <v>-12.80621425514092</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.348369380547156</v>
       </c>
       <c r="E93">
-        <v>-33.51332945568168</v>
+        <v>-33.28129950447667</v>
       </c>
       <c r="F93">
-        <v>-5.61581755043842</v>
+        <v>-5.109921980405123</v>
       </c>
       <c r="G93">
-        <v>-11.42702774129839</v>
+        <v>-12.16450472889967</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.445649057319498</v>
       </c>
       <c r="E94">
-        <v>-35.74651244900927</v>
+        <v>-34.45935711096507</v>
       </c>
       <c r="F94">
-        <v>-5.762631590338785</v>
+        <v>-4.661240090148381</v>
       </c>
       <c r="G94">
-        <v>-11.92047779610891</v>
+        <v>-11.52999563920634</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.545468438354186</v>
       </c>
       <c r="E95">
-        <v>-36.91961816917028</v>
+        <v>-38.29760790309732</v>
       </c>
       <c r="F95">
-        <v>-5.968954716088863</v>
+        <v>-5.084829903406923</v>
       </c>
       <c r="G95">
-        <v>-12.03310586590046</v>
+        <v>-11.27011781437355</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.646794047314623</v>
       </c>
       <c r="E96">
-        <v>-36.24596237578923</v>
+        <v>-40.23396527488114</v>
       </c>
       <c r="F96">
-        <v>-5.451359284858426</v>
+        <v>-5.929067168909262</v>
       </c>
       <c r="G96">
-        <v>-12.19650115153673</v>
+        <v>-12.94670056564543</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.748497311189782</v>
       </c>
       <c r="E97">
-        <v>-38.09991510605547</v>
+        <v>-40.82581192107661</v>
       </c>
       <c r="F97">
-        <v>-5.639952034718983</v>
+        <v>-5.44705508783348</v>
       </c>
       <c r="G97">
-        <v>-12.70039266697812</v>
+        <v>-12.26705549806968</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.851463325968044</v>
       </c>
       <c r="E98">
-        <v>-40.8138205219043</v>
+        <v>-42.51623013374086</v>
       </c>
       <c r="F98">
-        <v>-5.585235054294465</v>
+        <v>-5.464747358822471</v>
       </c>
       <c r="G98">
-        <v>-11.40542974220018</v>
+        <v>-11.83451286009066</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.95462330292013</v>
       </c>
       <c r="E99">
-        <v>-43.36973200809952</v>
+        <v>-41.53679592570288</v>
       </c>
       <c r="F99">
-        <v>-5.902715973458807</v>
+        <v>-6.157636929628923</v>
       </c>
       <c r="G99">
-        <v>-12.02097933759011</v>
+        <v>-13.27666595009013</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.06061601886891</v>
       </c>
       <c r="E100">
-        <v>-45.27823926473616</v>
+        <v>-46.12110148941381</v>
       </c>
       <c r="F100">
-        <v>-5.880294552967232</v>
+        <v>-6.908135725646769</v>
       </c>
       <c r="G100">
-        <v>-12.88257198800421</v>
+        <v>-12.24812248813058</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.164724363749858</v>
       </c>
       <c r="E101">
-        <v>-45.38574750191526</v>
+        <v>-48.68955005589926</v>
       </c>
       <c r="F101">
-        <v>-6.023240945463926</v>
+        <v>-7.190451206011167</v>
       </c>
       <c r="G101">
-        <v>-12.76221048383293</v>
+        <v>-14.37605177604454</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.273034993312944</v>
       </c>
       <c r="E102">
-        <v>-47.59088791995034</v>
+        <v>-48.68983874611725</v>
       </c>
       <c r="F102">
-        <v>-6.584007572258662</v>
+        <v>-6.674456180602938</v>
       </c>
       <c r="G102">
-        <v>-14.3408871613264</v>
+        <v>-13.39695793280509</v>
       </c>
     </row>
   </sheetData>
